--- a/booking_forms/038_guest_wi_fi_access_booking_form--booking_forms.xlsx
+++ b/booking_forms/038_guest_wi_fi_access_booking_form--booking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>policy_acknowledgment</t>
+          <t>policy_acknowledgment_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Policy Acknowledgment</t>
+          <t>Policy Acknowledgment 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>visit_duration</t>
+          <t>visit_duration_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Visit Duration</t>
+          <t>Visit Duration 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>policy_acknowledgment</t>
+          <t>policy_acknowledgment_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Policy Acknowledgment</t>
+          <t>Policy Acknowledgment 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="47" customWidth="1" min="2" max="2"/>
     <col width="47" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +1126,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>policy_acknowledgment_choices</t>
+          <t>policy_acknowledgment_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>policy_acknowledgment_choices</t>
+          <t>policy_acknowledgment_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1296,7 +1296,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>policy_acknowledgment_choices</t>
+          <t>policy_acknowledgment_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1313,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>policy_acknowledgment_choices</t>
+          <t>policy_acknowledgment_3_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
